--- a/out/add_lead_template.xlsx
+++ b/out/add_lead_template.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Desktop/Self Learing/Magic Carpet/magic-carpet-ui/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahavir.sancheti\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7544CB4A-BE13-3948-BDC5-B9484ED13570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{28CC2AEF-E6F4-4965-B54A-A05CD7DD7084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="15640" xr2:uid="{17133C78-3FDF-7841-A65D-898E8E5E469F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D3BE8528-7618-4F20-B1F0-9021A8171EEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,16 +38,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
-    <t>Name of Person</t>
+    <t>Name</t>
   </si>
   <si>
     <t>Email</t>
   </si>
   <si>
-    <t>Company Name</t>
-  </si>
-  <si>
-    <t>Industry Name </t>
+    <t>Current Company</t>
+  </si>
+  <si>
+    <t>Industry</t>
   </si>
   <si>
     <t>City</t>
@@ -59,38 +59,31 @@
     <t>LinkedIn URL</t>
   </si>
   <si>
-    <t>Personal Website</t>
-  </si>
-  <si>
-    <t>Target Products</t>
+    <t>Instagram URL</t>
+  </si>
+  <si>
+    <t>Twitter URL</t>
   </si>
   <si>
     <t>Facebook URL</t>
   </si>
   <si>
-    <t>Twitter URL</t>
-  </si>
-  <si>
-    <t>Instagram URL</t>
+    <t>Product IDs</t>
+  </si>
+  <si>
+    <t>Initial Note</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -116,7 +109,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -450,25 +445,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398B23CF-C868-F34B-9DB1-31CB6437ECF6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0BC6459-DF47-4319-B770-DBDCB4FA98A8}">
   <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.1640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -491,19 +472,19 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/out/add_lead_template.xlsx
+++ b/out/add_lead_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mahavir.sancheti\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28CC2AEF-E6F4-4965-B54A-A05CD7DD7084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92728972-9615-498C-8673-8F15DB91C78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D3BE8528-7618-4F20-B1F0-9021A8171EEB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Name</t>
   </si>
@@ -72,16 +72,54 @@
   </si>
   <si>
     <t>Initial Note</t>
+  </si>
+  <si>
+    <t>Vijay Harde</t>
+  </si>
+  <si>
+    <t>Tech</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>69a6e60e14d9cac23b902dcf</t>
+  </si>
+  <si>
+    <t>Mahindra</t>
+  </si>
+  <si>
+    <t>abc@gmail.com</t>
+  </si>
+  <si>
+    <t>Personal URL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -104,16 +142,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -446,10 +488,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0BC6459-DF47-4319-B770-DBDCB4FA98A8}">
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.36328125" customWidth="1"/>
+    <col min="12" max="12" width="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.1796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -481,13 +538,48 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
+    </row>
+    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="2"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{49AB2D8D-682F-204A-96FD-D17FB221200D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>